--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -9586,7 +9586,7 @@
         <v>115758693</v>
       </c>
       <c r="B75" t="n">
-        <v>95384</v>
+        <v>95386</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY144"/>
+  <dimension ref="A1:AY145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18036,6 +18036,130 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>118880153</v>
+      </c>
+      <c r="B145" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Bennarby, Upl</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>653046</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6675358</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Flera plantor tätt ihop på liten yta. Några blommande eller överblommade.</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Moa Volny</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Moa Volny</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -18041,7 +18041,7 @@
         <v>118880153</v>
       </c>
       <c r="B145" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY146"/>
+  <dimension ref="A1:AY151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18270,6 +18270,612 @@
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>120094042</v>
+      </c>
+      <c r="B147" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>652788</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6676314</v>
+      </c>
+      <c r="S147" t="n">
+        <v>4</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Annika Rastén, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>120094037</v>
+      </c>
+      <c r="B148" t="n">
+        <v>90399</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>6020</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Oljetagging</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Sistotrema raduloides</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Donk</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Lissmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>652767</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6676128</v>
+      </c>
+      <c r="S148" t="n">
+        <v>4</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Annika Rastén, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>120094034</v>
+      </c>
+      <c r="B149" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Lissmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>652812</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6675836</v>
+      </c>
+      <c r="S149" t="n">
+        <v>38</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Annika Rastén, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>120094035</v>
+      </c>
+      <c r="B150" t="n">
+        <v>80483</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>652789</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6676300</v>
+      </c>
+      <c r="S150" t="n">
+        <v>4</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Annika Rastén, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>120094052</v>
+      </c>
+      <c r="B151" t="n">
+        <v>91861</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Fållmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>652575</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6676580</v>
+      </c>
+      <c r="S151" t="n">
+        <v>4</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Annika Rastén, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY151"/>
+  <dimension ref="A1:AY152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18272,10 +18272,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120094042</v>
+        <v>120094034</v>
       </c>
       <c r="B147" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18288,40 +18288,49 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Lissmossen, Upl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>652788</v>
+        <v>652812</v>
       </c>
       <c r="R147" t="n">
-        <v>6676314</v>
+        <v>6675836</v>
       </c>
       <c r="S147" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -18350,7 +18359,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18360,7 +18369,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18369,7 +18378,6 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -18388,10 +18396,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120094037</v>
+        <v>120094035</v>
       </c>
       <c r="B148" t="n">
-        <v>90399</v>
+        <v>80483</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -18404,21 +18412,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6020</v>
+        <v>1049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -18427,14 +18435,14 @@
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Lissmossen, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>652767</v>
+        <v>652789</v>
       </c>
       <c r="R148" t="n">
-        <v>6676128</v>
+        <v>6676300</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -18466,7 +18474,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18476,12 +18484,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18490,24 +18493,8 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18524,10 +18511,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120094034</v>
+        <v>120094052</v>
       </c>
       <c r="B149" t="n">
-        <v>57463</v>
+        <v>91861</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18536,53 +18523,44 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Lissmossen, Upl</t>
+          <t>Fållmyren, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>652812</v>
+        <v>652575</v>
       </c>
       <c r="R149" t="n">
-        <v>6675836</v>
+        <v>6676580</v>
       </c>
       <c r="S149" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -18611,7 +18589,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18621,7 +18599,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18648,10 +18626,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120094035</v>
+        <v>120094037</v>
       </c>
       <c r="B150" t="n">
-        <v>80483</v>
+        <v>90399</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18664,21 +18642,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1049</v>
+        <v>6020</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -18687,14 +18665,14 @@
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Lissmossen, Upl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>652789</v>
+        <v>652767</v>
       </c>
       <c r="R150" t="n">
-        <v>6676300</v>
+        <v>6676128</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -18726,7 +18704,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18736,7 +18714,12 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18745,8 +18728,24 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
@@ -18763,10 +18762,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120094052</v>
+        <v>120094042</v>
       </c>
       <c r="B151" t="n">
-        <v>91861</v>
+        <v>90562</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18775,25 +18774,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -18802,14 +18801,14 @@
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Fållmyren, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>652575</v>
+        <v>652788</v>
       </c>
       <c r="R151" t="n">
-        <v>6676580</v>
+        <v>6676314</v>
       </c>
       <c r="S151" t="n">
         <v>4</v>
@@ -18841,7 +18840,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18851,7 +18850,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18860,6 +18859,7 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -18875,6 +18875,146 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>120094048</v>
+      </c>
+      <c r="B152" t="n">
+        <v>90948</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>715</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Finporing</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Gloeoporus pannocinctus</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Romell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Fållmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>652588</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6676579</v>
+      </c>
+      <c r="S152" t="n">
+        <v>4</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>På undersidan av tallåga med hälften av barken kvar. Luktar syrligt. Ganska mjuk. Johan tar kollekt och mikroskoperar.</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Annika Rastén, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -18511,10 +18511,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120094052</v>
+        <v>120094037</v>
       </c>
       <c r="B149" t="n">
-        <v>91861</v>
+        <v>90399</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18523,25 +18523,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5964</v>
+        <v>6020</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -18550,14 +18550,14 @@
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Fållmyren, Upl</t>
+          <t>Lissmossen, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>652575</v>
+        <v>652767</v>
       </c>
       <c r="R149" t="n">
-        <v>6676580</v>
+        <v>6676128</v>
       </c>
       <c r="S149" t="n">
         <v>4</v>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18599,7 +18599,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18608,8 +18613,24 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
@@ -18626,10 +18647,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120094037</v>
+        <v>120094052</v>
       </c>
       <c r="B150" t="n">
-        <v>90399</v>
+        <v>91861</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18638,25 +18659,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6020</v>
+        <v>5964</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -18665,14 +18686,14 @@
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Lissmossen, Upl</t>
+          <t>Fållmyren, Upl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>652767</v>
+        <v>652575</v>
       </c>
       <c r="R150" t="n">
-        <v>6676128</v>
+        <v>6676580</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -18704,7 +18725,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18714,12 +18735,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18728,24 +18744,8 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -18272,10 +18272,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120094034</v>
+        <v>120094035</v>
       </c>
       <c r="B147" t="n">
-        <v>57463</v>
+        <v>80483</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18288,49 +18288,40 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Lissmossen, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>652812</v>
+        <v>652789</v>
       </c>
       <c r="R147" t="n">
-        <v>6675836</v>
+        <v>6676300</v>
       </c>
       <c r="S147" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -18359,7 +18350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18369,7 +18360,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18396,10 +18387,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120094035</v>
+        <v>120094037</v>
       </c>
       <c r="B148" t="n">
-        <v>80483</v>
+        <v>90399</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -18412,21 +18403,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1049</v>
+        <v>6020</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -18435,14 +18426,14 @@
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Lissmossen, Upl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>652789</v>
+        <v>652767</v>
       </c>
       <c r="R148" t="n">
-        <v>6676300</v>
+        <v>6676128</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -18474,7 +18465,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18484,7 +18475,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18493,8 +18489,24 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18511,10 +18523,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120094037</v>
+        <v>120094034</v>
       </c>
       <c r="B149" t="n">
-        <v>90399</v>
+        <v>57463</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18527,26 +18539,35 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6020</v>
+        <v>103021</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -18554,13 +18575,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>652767</v>
+        <v>652812</v>
       </c>
       <c r="R149" t="n">
-        <v>6676128</v>
+        <v>6675836</v>
       </c>
       <c r="S149" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -18589,7 +18610,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18599,12 +18620,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18613,24 +18629,8 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
@@ -18647,10 +18647,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120094052</v>
+        <v>120094042</v>
       </c>
       <c r="B150" t="n">
-        <v>91861</v>
+        <v>90562</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18659,25 +18659,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -18686,14 +18686,14 @@
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Fållmyren, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>652575</v>
+        <v>652788</v>
       </c>
       <c r="R150" t="n">
-        <v>6676580</v>
+        <v>6676314</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18744,6 +18744,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -18762,10 +18763,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120094042</v>
+        <v>120094048</v>
       </c>
       <c r="B151" t="n">
-        <v>90562</v>
+        <v>90948</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18774,25 +18775,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>715</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -18801,14 +18802,14 @@
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Fållmyren, Upl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>652788</v>
+        <v>652588</v>
       </c>
       <c r="R151" t="n">
-        <v>6676314</v>
+        <v>6676579</v>
       </c>
       <c r="S151" t="n">
         <v>4</v>
@@ -18840,7 +18841,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18850,7 +18851,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>På undersidan av tallåga med hälften av barken kvar. Luktar syrligt. Ganska mjuk. Johan tar kollekt och mikroskoperar.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18859,9 +18865,28 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG151" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -18878,10 +18903,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120094048</v>
+        <v>120094045</v>
       </c>
       <c r="B152" t="n">
-        <v>90948</v>
+        <v>90763</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18894,21 +18919,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>715</v>
+        <v>1106</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18917,14 +18942,14 @@
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Fållmyren, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>652588</v>
+        <v>652719</v>
       </c>
       <c r="R152" t="n">
-        <v>6676579</v>
+        <v>6676369</v>
       </c>
       <c r="S152" t="n">
         <v>4</v>
@@ -18956,7 +18981,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18966,12 +18991,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>På undersidan av tallåga med hälften av barken kvar. Luktar syrligt. Ganska mjuk. Johan tar kollekt och mikroskoperar.</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18987,21 +19007,6 @@
       </c>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -18272,10 +18272,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120094035</v>
+        <v>120094037</v>
       </c>
       <c r="B147" t="n">
-        <v>80483</v>
+        <v>90399</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18288,21 +18288,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1049</v>
+        <v>6020</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -18311,14 +18311,14 @@
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Lissmossen, Upl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>652789</v>
+        <v>652767</v>
       </c>
       <c r="R147" t="n">
-        <v>6676300</v>
+        <v>6676128</v>
       </c>
       <c r="S147" t="n">
         <v>4</v>
@@ -18350,7 +18350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18360,7 +18360,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18369,8 +18374,24 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -18387,10 +18408,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120094037</v>
+        <v>120094035</v>
       </c>
       <c r="B148" t="n">
-        <v>90399</v>
+        <v>80483</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -18403,21 +18424,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6020</v>
+        <v>1049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -18426,14 +18447,14 @@
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Lissmossen, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>652767</v>
+        <v>652789</v>
       </c>
       <c r="R148" t="n">
-        <v>6676128</v>
+        <v>6676300</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -18465,7 +18486,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18475,12 +18496,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18489,24 +18505,8 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -18763,10 +18763,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120094048</v>
+        <v>120094045</v>
       </c>
       <c r="B151" t="n">
-        <v>90948</v>
+        <v>90763</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18779,21 +18779,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>715</v>
+        <v>1106</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -18802,14 +18802,14 @@
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Fållmyren, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>652588</v>
+        <v>652719</v>
       </c>
       <c r="R151" t="n">
-        <v>6676579</v>
+        <v>6676369</v>
       </c>
       <c r="S151" t="n">
         <v>4</v>
@@ -18841,7 +18841,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18851,12 +18851,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>På undersidan av tallåga med hälften av barken kvar. Luktar syrligt. Ganska mjuk. Johan tar kollekt och mikroskoperar.</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18872,21 +18867,6 @@
       </c>
       <c r="AG151" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
@@ -18903,10 +18883,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120094045</v>
+        <v>120094048</v>
       </c>
       <c r="B152" t="n">
-        <v>90763</v>
+        <v>90966</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18919,21 +18899,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1106</v>
+        <v>715</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18942,14 +18922,14 @@
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Fållmyren, Upl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>652719</v>
+        <v>652588</v>
       </c>
       <c r="R152" t="n">
-        <v>6676369</v>
+        <v>6676579</v>
       </c>
       <c r="S152" t="n">
         <v>4</v>
@@ -18981,7 +18961,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18991,7 +18971,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>På undersidan av tallåga med hälften av barken kvar. Luktar syrligt. Ganska mjuk. Johan tar kollekt och mikroskoperar.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -19007,6 +18992,21 @@
       </c>
       <c r="AG152" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -18272,10 +18272,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120094037</v>
+        <v>120094034</v>
       </c>
       <c r="B147" t="n">
-        <v>90399</v>
+        <v>57473</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18288,26 +18288,35 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6020</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
@@ -18315,13 +18324,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>652767</v>
+        <v>652812</v>
       </c>
       <c r="R147" t="n">
-        <v>6676128</v>
+        <v>6675836</v>
       </c>
       <c r="S147" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -18350,7 +18359,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18360,12 +18369,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18374,24 +18378,8 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -18411,7 +18399,7 @@
         <v>120094035</v>
       </c>
       <c r="B148" t="n">
-        <v>80483</v>
+        <v>80499</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -18523,10 +18511,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120094034</v>
+        <v>120094037</v>
       </c>
       <c r="B149" t="n">
-        <v>57463</v>
+        <v>90416</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18539,35 +18527,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103021</v>
+        <v>6020</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Donk</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -18575,13 +18554,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>652812</v>
+        <v>652767</v>
       </c>
       <c r="R149" t="n">
-        <v>6675836</v>
+        <v>6676128</v>
       </c>
       <c r="S149" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -18610,7 +18589,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18620,7 +18599,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18629,8 +18613,24 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
@@ -18650,7 +18650,7 @@
         <v>120094042</v>
       </c>
       <c r="B150" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>120094045</v>
       </c>
       <c r="B151" t="n">
-        <v>90763</v>
+        <v>90781</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -18272,10 +18272,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120094034</v>
+        <v>120094035</v>
       </c>
       <c r="B147" t="n">
-        <v>57473</v>
+        <v>80499</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18288,49 +18288,40 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Lissmossen, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>652812</v>
+        <v>652789</v>
       </c>
       <c r="R147" t="n">
-        <v>6675836</v>
+        <v>6676300</v>
       </c>
       <c r="S147" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -18359,7 +18350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18369,7 +18360,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18396,10 +18387,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120094035</v>
+        <v>120094037</v>
       </c>
       <c r="B148" t="n">
-        <v>80499</v>
+        <v>90416</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -18412,21 +18403,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1049</v>
+        <v>6020</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -18435,14 +18426,14 @@
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Lissmossen, Upl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>652789</v>
+        <v>652767</v>
       </c>
       <c r="R148" t="n">
-        <v>6676300</v>
+        <v>6676128</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -18474,7 +18465,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18484,7 +18475,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18493,8 +18489,24 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18511,10 +18523,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120094037</v>
+        <v>120094042</v>
       </c>
       <c r="B149" t="n">
-        <v>90416</v>
+        <v>90580</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18527,21 +18539,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6020</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -18550,14 +18562,14 @@
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Lissmossen, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>652767</v>
+        <v>652788</v>
       </c>
       <c r="R149" t="n">
-        <v>6676128</v>
+        <v>6676314</v>
       </c>
       <c r="S149" t="n">
         <v>4</v>
@@ -18589,7 +18601,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18599,12 +18611,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18616,21 +18623,6 @@
       <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
@@ -18647,10 +18639,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120094042</v>
+        <v>120094034</v>
       </c>
       <c r="B150" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18663,40 +18655,49 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Lissmossen, Upl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>652788</v>
+        <v>652812</v>
       </c>
       <c r="R150" t="n">
-        <v>6676314</v>
+        <v>6675836</v>
       </c>
       <c r="S150" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18725,7 +18726,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18735,7 +18736,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18744,7 +18745,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -18272,10 +18272,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120094035</v>
+        <v>120094042</v>
       </c>
       <c r="B147" t="n">
-        <v>80499</v>
+        <v>90580</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18288,21 +18288,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -18315,10 +18315,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>652789</v>
+        <v>652788</v>
       </c>
       <c r="R147" t="n">
-        <v>6676300</v>
+        <v>6676314</v>
       </c>
       <c r="S147" t="n">
         <v>4</v>
@@ -18350,7 +18350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18369,6 +18369,7 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -18387,10 +18388,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120094037</v>
+        <v>120094035</v>
       </c>
       <c r="B148" t="n">
-        <v>90416</v>
+        <v>80499</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -18403,21 +18404,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6020</v>
+        <v>1049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -18426,14 +18427,14 @@
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Lissmossen, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>652767</v>
+        <v>652789</v>
       </c>
       <c r="R148" t="n">
-        <v>6676128</v>
+        <v>6676300</v>
       </c>
       <c r="S148" t="n">
         <v>4</v>
@@ -18465,7 +18466,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18475,12 +18476,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18489,24 +18485,8 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18523,10 +18503,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120094042</v>
+        <v>120094037</v>
       </c>
       <c r="B149" t="n">
-        <v>90580</v>
+        <v>90416</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18539,21 +18519,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>6020</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -18562,14 +18542,14 @@
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Lissmossen, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>652788</v>
+        <v>652767</v>
       </c>
       <c r="R149" t="n">
-        <v>6676314</v>
+        <v>6676128</v>
       </c>
       <c r="S149" t="n">
         <v>4</v>
@@ -18601,7 +18581,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18611,7 +18591,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18623,6 +18608,21 @@
       <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -18272,10 +18272,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120094042</v>
+        <v>120094037</v>
       </c>
       <c r="B147" t="n">
-        <v>90580</v>
+        <v>90416</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18288,21 +18288,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>6020</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -18311,14 +18311,14 @@
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Lissmossen, Upl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>652788</v>
+        <v>652767</v>
       </c>
       <c r="R147" t="n">
-        <v>6676314</v>
+        <v>6676128</v>
       </c>
       <c r="S147" t="n">
         <v>4</v>
@@ -18350,7 +18350,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18360,7 +18360,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18372,6 +18377,21 @@
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -18503,10 +18523,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120094037</v>
+        <v>120094042</v>
       </c>
       <c r="B149" t="n">
-        <v>90416</v>
+        <v>90580</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18519,21 +18539,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6020</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -18542,14 +18562,14 @@
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Lissmossen, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>652767</v>
+        <v>652788</v>
       </c>
       <c r="R149" t="n">
-        <v>6676128</v>
+        <v>6676314</v>
       </c>
       <c r="S149" t="n">
         <v>4</v>
@@ -18581,7 +18601,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18591,12 +18611,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18608,21 +18623,6 @@
       <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -18523,10 +18523,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120094042</v>
+        <v>120094034</v>
       </c>
       <c r="B149" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18539,40 +18539,49 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Lissmossen, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>652788</v>
+        <v>652812</v>
       </c>
       <c r="R149" t="n">
-        <v>6676314</v>
+        <v>6675836</v>
       </c>
       <c r="S149" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -18601,7 +18610,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18611,7 +18620,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18620,7 +18629,6 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -18639,10 +18647,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120094034</v>
+        <v>120094042</v>
       </c>
       <c r="B150" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18655,49 +18663,40 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Lissmossen, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>652812</v>
+        <v>652788</v>
       </c>
       <c r="R150" t="n">
-        <v>6675836</v>
+        <v>6676314</v>
       </c>
       <c r="S150" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18726,7 +18725,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18736,7 +18735,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18745,6 +18744,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -7539,7 +7539,7 @@
         <v>111410448</v>
       </c>
       <c r="B58" t="n">
-        <v>5113</v>
+        <v>5168</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7548,32 +7548,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100526</v>
+        <v>102204</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -7589,10 +7585,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>652958.5506333391</v>
+        <v>652959</v>
       </c>
       <c r="R58" t="n">
-        <v>6675625.7669597</v>
+        <v>6675626</v>
       </c>
       <c r="S58" t="n">
         <v>8</v>
@@ -7637,14 +7633,40 @@
           <t>15:40</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Felbestämd till bronshjon vid fyndtillfället, korrigerat drygt ett år senare efter avstämning med kunnigare bekant.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Senvuxet, stående, klent träd.</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies # Senvuxet, stående, klent träd.</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -18430,10 +18430,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120094035</v>
+        <v>120094034</v>
       </c>
       <c r="B148" t="n">
-        <v>80499</v>
+        <v>57473</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -18446,40 +18446,49 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Lissmossen, Upl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>652789</v>
+        <v>652812</v>
       </c>
       <c r="R148" t="n">
-        <v>6676300</v>
+        <v>6675836</v>
       </c>
       <c r="S148" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -18508,7 +18517,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18518,7 +18527,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18545,10 +18554,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120094034</v>
+        <v>120094042</v>
       </c>
       <c r="B149" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18561,49 +18570,40 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Lissmossen, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>652812</v>
+        <v>652788</v>
       </c>
       <c r="R149" t="n">
-        <v>6675836</v>
+        <v>6676314</v>
       </c>
       <c r="S149" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18642,7 +18642,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18651,6 +18651,7 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -18669,10 +18670,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120094042</v>
+        <v>120094035</v>
       </c>
       <c r="B150" t="n">
-        <v>90580</v>
+        <v>80499</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18685,21 +18686,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -18712,10 +18713,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>652788</v>
+        <v>652789</v>
       </c>
       <c r="R150" t="n">
-        <v>6676314</v>
+        <v>6676300</v>
       </c>
       <c r="S150" t="n">
         <v>4</v>
@@ -18747,7 +18748,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18757,7 +18758,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18766,7 +18767,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -18294,10 +18294,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120094037</v>
+        <v>120094035</v>
       </c>
       <c r="B147" t="n">
-        <v>90416</v>
+        <v>80499</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18310,21 +18310,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6020</v>
+        <v>1049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -18333,14 +18333,14 @@
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Lissmossen, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>652767</v>
+        <v>652789</v>
       </c>
       <c r="R147" t="n">
-        <v>6676128</v>
+        <v>6676300</v>
       </c>
       <c r="S147" t="n">
         <v>4</v>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18382,12 +18382,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18396,24 +18391,8 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -18430,10 +18409,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120094034</v>
+        <v>120094037</v>
       </c>
       <c r="B148" t="n">
-        <v>57473</v>
+        <v>90416</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -18446,35 +18425,26 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>103021</v>
+        <v>6020</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Donk</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
@@ -18482,13 +18452,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>652812</v>
+        <v>652767</v>
       </c>
       <c r="R148" t="n">
-        <v>6675836</v>
+        <v>6676128</v>
       </c>
       <c r="S148" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -18517,7 +18487,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18527,7 +18497,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>På barklös granlåga. Gula, långa, lite tufsiga taggar. Stark kemisk, lite fruktig lukt.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18536,8 +18511,24 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18670,10 +18661,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120094035</v>
+        <v>120094034</v>
       </c>
       <c r="B150" t="n">
-        <v>80499</v>
+        <v>57473</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18686,40 +18677,49 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Lissmossen, Upl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>652789</v>
+        <v>652812</v>
       </c>
       <c r="R150" t="n">
-        <v>6676300</v>
+        <v>6675836</v>
       </c>
       <c r="S150" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD150" t="b">

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -18664,11 +18664,11 @@
         <v>120094034</v>
       </c>
       <c r="B150" t="n">
-        <v>57473</v>
+        <v>57631</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">

--- a/artfynd/A 23606-2023 artfynd.xlsx
+++ b/artfynd/A 23606-2023 artfynd.xlsx
@@ -18664,7 +18664,7 @@
         <v>120094034</v>
       </c>
       <c r="B150" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
